--- a/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
+++ b/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
@@ -3348,15 +3348,15 @@
   <dimension ref="A1:AO400"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.86328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="52.90234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.96484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="37.5859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.9296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.47265625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.87890625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.2734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.7265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="67.57421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.44921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.0390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65234375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3367,27 +3367,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="36.22265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.4609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.86328125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="91.51171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.32421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.52734375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="21.87890625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="38.34375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.06640625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.73046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.28515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.6875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.54296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.7421875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.12890625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="87.265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.86328125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.3671875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.2109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.85546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.23828125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.13671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="54.8984375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="68.76171875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.4453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="52.3515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="65.5703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="30.9375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7993,7 +7993,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
+++ b/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
@@ -376,7 +376,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1058,7 +1058,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1136,7 +1136,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1209,7 +1209,7 @@
     <t>Composition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1246,7 +1246,7 @@
     <t>Composition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1525,7 +1525,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1753,7 +1753,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -2850,13 +2850,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -2942,7 +2942,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -3010,7 +3010,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>

--- a/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
+++ b/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
@@ -3515,7 +3515,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>171</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>194</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>244</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>255</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>264</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>276</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>288</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>305</v>
       </c>
@@ -9484,7 +9484,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>312</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>407</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>418</v>
       </c>
@@ -13696,7 +13696,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>443</v>
       </c>
@@ -47894,7 +47894,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="381" hidden="true">
+    <row r="381">
       <c r="A381" t="s" s="2">
         <v>906</v>
       </c>
@@ -50242,12 +50242,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO400">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
+++ b/docs/StructureDefinition-BRRegulacaoAssistencial.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
